--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-07_duzeltici_faaliyet_istek_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-07_duzeltici_faaliyet_istek_formu.xlsx
@@ -20886,7 +20886,8 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="0" differentOddEven="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-07&amp;C&amp;"Arial,Regular"&amp;11Düzeltici Faaliyet İstek Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Faaliyet ve kapanış kanıtı tanımları düzeltildi; süreler risk ve müşteri şartına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
